--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104555_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104555_W11.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8213</v>
+        <v>6.884</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5532</v>
+        <v>4.2401</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2681</v>
+        <v>2.6439</v>
       </c>
       <c r="G2" t="n">
-        <v>7.7344</v>
+        <v>7.6932</v>
       </c>
       <c r="H2" t="n">
-        <v>7.6972</v>
+        <v>7.6699</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0372</v>
+        <v>0.0232</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7392</v>
+        <v>6.6699</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5662</v>
+        <v>6.522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1731</v>
+        <v>0.1478</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9952</v>
+        <v>1.0233</v>
       </c>
       <c r="N2" t="n">
-        <v>1.131</v>
+        <v>1.1479</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2423</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2994</v>
+        <v>1.0821</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5417</v>
+        <v>-0.2005</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7</v>
+        <v>5.5514</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9973</v>
+        <v>3.9274</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7027</v>
+        <v>1.624</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0232</v>
+        <v>1.0055</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3796</v>
+        <v>3.3668</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.3564</v>
+        <v>-2.3613</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2939</v>
+        <v>1.2441</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3972</v>
+        <v>3.3677</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.1033</v>
+        <v>-2.1236</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2707</v>
+        <v>-0.2386</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3157</v>
+        <v>1.1801</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2571</v>
+        <v>0.7336</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5728</v>
+        <v>0.4465</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.576</v>
+        <v>4.344</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6168</v>
+        <v>3.917</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9593</v>
+        <v>0.4271</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.7928</v>
+        <v>3.8499</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6622</v>
+        <v>2.0535</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1306</v>
+        <v>1.7964</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.6257</v>
+        <v>3.5758</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.1006</v>
+        <v>1.9822</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5251</v>
+        <v>1.5935</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8329</v>
+        <v>0.2741</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4383</v>
+        <v>0.0713</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3946</v>
+        <v>0.2028</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>6.6468</v>
+        <v>0.2845</v>
       </c>
       <c r="T4" t="n">
-        <v>6.2425</v>
+        <v>0.3412</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4043</v>
+        <v>-0.0567</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-0.4733</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1553</v>
+        <v>4.2669</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0313</v>
+        <v>2.2692</v>
       </c>
       <c r="F5" t="n">
-        <v>2.124</v>
+        <v>1.9977</v>
       </c>
       <c r="G5" t="n">
-        <v>4.5459</v>
+        <v>4.5549</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7257</v>
+        <v>1.7288</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8202</v>
+        <v>2.8261</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4921</v>
+        <v>3.4751</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0665</v>
+        <v>1.0547</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4256</v>
+        <v>2.4204</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0538</v>
+        <v>1.0798</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2899</v>
+        <v>1.3949</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8075</v>
+        <v>1.0704</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4824</v>
+        <v>0.3245</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1644</v>
+        <v>2.0301</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1064</v>
+        <v>2.2347</v>
       </c>
       <c r="F6" t="n">
-        <v>0.058</v>
+        <v>-0.2046</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8525</v>
+        <v>1.7492</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0533</v>
+        <v>0.4216</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7992</v>
+        <v>1.3276</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5933</v>
+        <v>1.4314</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9914</v>
+        <v>0.7239</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6019</v>
+        <v>0.7075</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2592</v>
+        <v>0.3178</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0619</v>
+        <v>-0.3023</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1973</v>
+        <v>0.6201</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8865</v>
+        <v>1.5493</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4869</v>
+        <v>0.8033</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3995</v>
+        <v>0.746</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4822</v>
+        <v>-2.1789</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4822</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3375</v>
+        <v>0.9364</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3879</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0504</v>
+        <v>1.7786</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7306</v>
+        <v>-2.7857</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4111</v>
+        <v>-2.6624</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3195</v>
+        <v>-0.1233</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4363</v>
+        <v>-3.6498</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7272999999999999</v>
+        <v>-3.1208</v>
       </c>
       <c r="L7" t="n">
-        <v>0.709</v>
+        <v>-0.529</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2943</v>
+        <v>0.8641</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3162</v>
+        <v>0.4584</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6105</v>
+        <v>0.4057</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8849</v>
+        <v>2.9905</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0484</v>
+        <v>2.8076</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9333</v>
+        <v>0.1829</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8343</v>
+        <v>-0.9535</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1223</v>
+        <v>-1.485</v>
       </c>
       <c r="F8" t="n">
-        <v>0.288</v>
+        <v>0.5315</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5613</v>
+        <v>-0.6923</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.476</v>
+        <v>-0.1864</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0852</v>
+        <v>-0.506</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3469</v>
+        <v>-0.4101</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8294</v>
+        <v>-0.5591</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4824</v>
+        <v>0.1489</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2143</v>
+        <v>-0.2822</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.3727</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5676</v>
+        <v>-0.6549</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>2.725</v>
+        <v>0.1941</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1716</v>
+        <v>0.3412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5535</v>
+        <v>-0.1471</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7712</v>
+        <v>-0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3214</v>
+        <v>0.8603</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8275</v>
+        <v>-2.1546</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4182</v>
+        <v>-2.4809</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5906</v>
+        <v>0.3263</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6973</v>
+        <v>-2.5583</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1803</v>
+        <v>-2.4812</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.517</v>
+        <v>-0.0771</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3915</v>
+        <v>-1.3722</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-1.8486</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1493</v>
+        <v>0.4764</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3057</v>
+        <v>-1.1861</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3605</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6663</v>
+        <v>-0.5535</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6766</v>
+        <v>1.4053</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6261</v>
+        <v>0.852</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0505</v>
+        <v>0.5532</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8678</v>
+        <v>0.3155</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3441</v>
+        <v>-2.7742</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1468</v>
+        <v>-1.6811</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1973</v>
+        <v>-1.0931</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4298</v>
+        <v>-1.4246</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3103</v>
+        <v>-0.3075</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="K10" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6954</v>
+        <v>-0.6866</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4606</v>
+        <v>0.1057</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2782</v>
+        <v>0.195</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1824</v>
+        <v>-0.0893</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5766</v>
+        <v>-3.5599</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.928</v>
+        <v>-3.9336</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3513</v>
+        <v>0.3737</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8266</v>
+        <v>-3.8455</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.766</v>
+        <v>-1.7745</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0605</v>
+        <v>-2.071</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8199</v>
+        <v>-2.8578</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6793</v>
+        <v>-0.697</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1406</v>
+        <v>-2.1608</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0066</v>
+        <v>-0.9877</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5232</v>
+        <v>0.5133</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9739</v>
+        <v>0.0624</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4506</v>
+        <v>0.4509</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.172</v>
+        <v>14.5706</v>
       </c>
       <c r="E12" t="n">
-        <v>5.077599999999998</v>
+        <v>6.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>8.0943</v>
+        <v>8.405100000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5788</v>
+        <v>7.546300000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>7.8721</v>
+        <v>7.8286</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2931000000000004</v>
+        <v>-0.2825000000000004</v>
       </c>
       <c r="J12" t="n">
-        <v>7.6364</v>
+        <v>7.3685</v>
       </c>
       <c r="K12" t="n">
-        <v>7.650499999999999</v>
+        <v>7.4767</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.01409999999999956</v>
+        <v>-0.1085000000000012</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.05729999999999968</v>
+        <v>0.1779000000000004</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2215</v>
+        <v>0.3519000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2789999999999999</v>
+        <v>-0.1741000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.7441</v>
+        <v>-14.7961</v>
       </c>
       <c r="R12" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S12" t="n">
-        <v>9.0731</v>
+        <v>10.4993</v>
       </c>
       <c r="T12" t="n">
-        <v>6.850399999999999</v>
+        <v>8.2888</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2228</v>
+        <v>2.2104</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.346</v>
+        <v>-2.3366</v>
       </c>
       <c r="W12" t="n">
-        <v>5.334899999999999</v>
+        <v>5.3044</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.681100000000001</v>
+        <v>-7.641199999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8286</v>
+        <v>2.6088</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5197</v>
+        <v>3.0277</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3088</v>
+        <v>-0.4189</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3373</v>
+        <v>1.5264</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2467</v>
+        <v>0.2437</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0906</v>
+        <v>1.2827</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0699</v>
+        <v>3.2036</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3739</v>
+        <v>1.3789</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3039</v>
+        <v>1.8246</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2674</v>
+        <v>-1.6772</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1272</v>
+        <v>-1.1353</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3946</v>
+        <v>-0.5419</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3571</v>
+        <v>-0.4623</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4498</v>
+        <v>0.2598</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0927</v>
+        <v>-0.7221</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1759</v>
+        <v>1.2794</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8079</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.632</v>
+        <v>0.4241</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5145</v>
+        <v>0.3421</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2351</v>
+        <v>0.2497</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2795</v>
+        <v>0.0924</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2139</v>
+        <v>0.052</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3853</v>
+        <v>0.3652</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8285</v>
+        <v>-0.3132</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6993</v>
+        <v>0.2901</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1503</v>
+        <v>-0.1155</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.549</v>
+        <v>0.4057</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8849</v>
+        <v>-0.2009</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0212</v>
+        <v>0.8033</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9061</v>
+        <v>-1.0042</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4808</v>
+        <v>1.1243</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6057</v>
+        <v>1.0886</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1249</v>
+        <v>0.0357</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4781</v>
+        <v>-0.4799</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6349</v>
+        <v>-1.6342</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8399</v>
+        <v>0.8089</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6101</v>
+        <v>-0.628</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4499</v>
+        <v>1.4369</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3179</v>
+        <v>-1.2888</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0684</v>
+        <v>-0.2788</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5293</v>
+        <v>0.06</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4609</v>
+        <v>-0.3388</v>
       </c>
       <c r="V15" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7876</v>
+        <v>0.9348</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3016</v>
+        <v>0.3981</v>
       </c>
       <c r="F16" t="n">
-        <v>0.486</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3746</v>
+        <v>0.3745</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5266</v>
+        <v>0.5311</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3322</v>
+        <v>-0.343</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6778</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2604</v>
+        <v>-0.2309</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3176</v>
+        <v>1.3187</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0729</v>
+        <v>-0.5995</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.1126</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.523</v>
+        <v>-0.4869</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4885</v>
+        <v>-0.4797</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8045</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3225</v>
+        <v>0.3248</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4953</v>
+        <v>1.4709</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9382</v>
+        <v>0.9201</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9838</v>
+        <v>-1.9506</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7493</v>
+        <v>-1.7246</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7451</v>
+        <v>-1.2776</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3912</v>
+        <v>-0.9203</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3539</v>
+        <v>-0.3573</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1691</v>
+        <v>-1.5809</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0496</v>
+        <v>0.1173</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8804999999999999</v>
+        <v>-1.6982</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8297</v>
+        <v>3.37</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.5604</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1861</v>
+        <v>3.9305</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.514</v>
+        <v>3.3533</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0906</v>
+        <v>0.1444</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4234</v>
+        <v>3.2089</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3157</v>
+        <v>0.0167</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.553</v>
+        <v>-0.7048</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2373</v>
+        <v>0.7215</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1558</v>
+        <v>-1.9313</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3206</v>
+        <v>-0.7321</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1649</v>
+        <v>-1.1992</v>
       </c>
       <c r="V18" t="n">
-        <v>1.639</v>
+        <v>-2.3367</v>
       </c>
       <c r="W18" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6368</v>
+        <v>-1.9824</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3585</v>
+        <v>-1.6127</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2783</v>
+        <v>-0.3698</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6512</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1267</v>
+        <v>1.1395</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7779</v>
+        <v>-1.7771</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6659</v>
+        <v>-0.6831</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5066</v>
+        <v>1.4996</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.1725</v>
+        <v>-2.1827</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0148</v>
+        <v>0.0456</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3798</v>
+        <v>-0.3601</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0271</v>
+        <v>-1.3936</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4657</v>
+        <v>-0.7019</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5614</v>
+        <v>-0.6917</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2725</v>
+        <v>-2.097</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.524</v>
+        <v>-1.4214</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7486</v>
+        <v>-0.6756</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8606</v>
+        <v>-1.8647</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1435</v>
+        <v>-1.144</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1762</v>
+        <v>-1.1913</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4644</v>
+        <v>-0.4761</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6844</v>
+        <v>-0.6734</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6388</v>
+        <v>-0.4599</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.291</v>
+        <v>-0.2298</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3821</v>
+        <v>-2.4233</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4221</v>
+        <v>-1.3997</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9599</v>
+        <v>-1.0236</v>
       </c>
       <c r="G21" t="n">
-        <v>3.3777</v>
+        <v>-2.0347</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5672</v>
+        <v>-2.7113</v>
       </c>
       <c r="I21" t="n">
-        <v>3.9449</v>
+        <v>0.6766</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3947</v>
+        <v>-1.0037</v>
       </c>
       <c r="K21" t="n">
-        <v>0.159</v>
+        <v>-1.7484</v>
       </c>
       <c r="L21" t="n">
-        <v>3.2357</v>
+        <v>0.7447</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.017</v>
+        <v>-1.031</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7261</v>
+        <v>-0.9629</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7091</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.7332</v>
+        <v>-0.2764</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3217</v>
+        <v>0.0624</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4115</v>
+        <v>-0.3388</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.3461</v>
+        <v>-1.7057</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.4584</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3461</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0095</v>
+        <v>-2.4738</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2043</v>
+        <v>-2.9155</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8052</v>
+        <v>0.4417</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0437</v>
+        <v>-1.826</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7128</v>
+        <v>-0.6434</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6691</v>
+        <v>-1.1826</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9893</v>
+        <v>-1.5412</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7357</v>
+        <v>-0.1109</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7463</v>
+        <v>-1.4303</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0543</v>
+        <v>-0.2847</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9771</v>
+        <v>-0.5325</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0772</v>
+        <v>0.2477</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8505</v>
+        <v>-1.1439</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7652</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0853</v>
+        <v>-0.6394</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7032</v>
+        <v>1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4498</v>
+        <v>1.6342</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.901999999999999</v>
+        <v>-7.9669</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.2208</v>
+        <v>-6.4301</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6812</v>
+        <v>-1.5368</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.8314</v>
+        <v>-5.8367</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.9206</v>
+        <v>-2.9182</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9108</v>
+        <v>-2.9185</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.2784</v>
+        <v>-4.3042</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2898</v>
+        <v>-2.3</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9886</v>
+        <v>-2.0042</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.553</v>
+        <v>-1.5325</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0971</v>
+        <v>-1.1499</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>-0.0073</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2624</v>
+        <v>-1.1425</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.172</v>
+        <v>-13.1765</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.0943</v>
+        <v>-8.405000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.0778</v>
+        <v>-4.7715</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.5791</v>
+        <v>-7.5463</v>
       </c>
       <c r="H24" t="n">
-        <v>-7.8721</v>
+        <v>-7.8287</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2930999999999999</v>
+        <v>0.2825000000000006</v>
       </c>
       <c r="J24" t="n">
-        <v>0.05769999999999964</v>
+        <v>-0.1777999999999995</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2215000000000003</v>
+        <v>-0.3518999999999997</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2789999999999999</v>
+        <v>0.1741000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.636300000000001</v>
+        <v>-7.368399999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.6505</v>
+        <v>-7.4769</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01419999999999977</v>
+        <v>0.1083999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.6101</v>
+        <v>-13.6578</v>
       </c>
       <c r="R24" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.0732</v>
+        <v>-9.1053</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.2228</v>
+        <v>-2.2105</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.8505</v>
+        <v>-6.894699999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W24" t="n">
-        <v>7.6811</v>
+        <v>7.641199999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.3351</v>
+        <v>-5.3045</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104555_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104555_W11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-7.641199999999999</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104555_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-5.3045</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
